--- a/Daily_Report/Top 7 broker List with its Turnover 2024-07-09.xlsx
+++ b/Daily_Report/Top 7 broker List with its Turnover 2024-07-09.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="279">
   <si>
     <t>Date: 2024-07-09</t>
   </si>
@@ -68,18 +68,18 @@
     <t>Linch Stock Market Limited</t>
   </si>
   <si>
+    <t>Stock Broker Opal Securities Investment Pvt. Limited</t>
+  </si>
+  <si>
+    <t>Imperial Securities Co .Pvt.Limited</t>
+  </si>
+  <si>
     <t>Vision Securities Pvt.Limited</t>
   </si>
   <si>
-    <t>Imperial Securities Co .Pvt.Limited</t>
-  </si>
-  <si>
     <t>Dynamic Money Managers Securities Pvt.Ltd</t>
   </si>
   <si>
-    <t>Araya Tara Investment And Securities Pvt. Ltd.</t>
-  </si>
-  <si>
     <t>58</t>
   </si>
   <si>
@@ -89,79 +89,76 @@
     <t>41</t>
   </si>
   <si>
+    <t>45</t>
+  </si>
+  <si>
     <t>34</t>
   </si>
   <si>
-    <t>45</t>
-  </si>
-  <si>
     <t>44</t>
   </si>
   <si>
-    <t>57</t>
-  </si>
-  <si>
-    <t>691,800,605.3</t>
-  </si>
-  <si>
-    <t>394,907,898.5</t>
-  </si>
-  <si>
-    <t>389,599,427.7</t>
-  </si>
-  <si>
-    <t>388,885,801.1</t>
-  </si>
-  <si>
-    <t>361,771,703.95</t>
-  </si>
-  <si>
-    <t>350,355,397.0</t>
-  </si>
-  <si>
-    <t>293,325,417.06</t>
-  </si>
-  <si>
-    <t>331,702,980.5</t>
-  </si>
-  <si>
-    <t>198,764,572.0</t>
-  </si>
-  <si>
-    <t>180,362,169.5</t>
-  </si>
-  <si>
-    <t>160,367,276.5</t>
-  </si>
-  <si>
-    <t>190,468,397.45</t>
-  </si>
-  <si>
-    <t>175,214,299.8</t>
-  </si>
-  <si>
-    <t>157,862,565.69</t>
-  </si>
-  <si>
-    <t>360,097,624.8</t>
-  </si>
-  <si>
-    <t>196,143,326.5</t>
-  </si>
-  <si>
-    <t>209,237,258.2</t>
-  </si>
-  <si>
-    <t>228,518,524.6</t>
-  </si>
-  <si>
-    <t>171,303,306.5</t>
-  </si>
-  <si>
-    <t>175,141,097.2</t>
-  </si>
-  <si>
-    <t>135,462,851.36</t>
+    <t>701,017,025.0</t>
+  </si>
+  <si>
+    <t>398,354,198.9</t>
+  </si>
+  <si>
+    <t>391,293,762.2</t>
+  </si>
+  <si>
+    <t>388,042,965.6</t>
+  </si>
+  <si>
+    <t>372,658,371.5</t>
+  </si>
+  <si>
+    <t>366,172,983.4</t>
+  </si>
+  <si>
+    <t>334,570,583.0</t>
+  </si>
+  <si>
+    <t>326,935,891.2</t>
+  </si>
+  <si>
+    <t>200,760,413.6</t>
+  </si>
+  <si>
+    <t>179,377,690.8</t>
+  </si>
+  <si>
+    <t>182,488,031.3</t>
+  </si>
+  <si>
+    <t>198,809,790.7</t>
+  </si>
+  <si>
+    <t>144,460,605.1</t>
+  </si>
+  <si>
+    <t>157,337,725.8</t>
+  </si>
+  <si>
+    <t>374,081,133.8</t>
+  </si>
+  <si>
+    <t>197,593,785.3</t>
+  </si>
+  <si>
+    <t>211,916,071.4</t>
+  </si>
+  <si>
+    <t>205,554,934.3</t>
+  </si>
+  <si>
+    <t>173,848,580.8</t>
+  </si>
+  <si>
+    <t>221,712,378.3</t>
+  </si>
+  <si>
+    <t>177,232,857.2</t>
   </si>
   <si>
     <t>Top 5 Buy</t>
@@ -182,7 +179,7 @@
     <t>NRN</t>
   </si>
   <si>
-    <t>43,254,378.1</t>
+    <t>43,284,798.7</t>
   </si>
   <si>
     <t>GMFBS</t>
@@ -191,22 +188,22 @@
     <t>35,765,562.79</t>
   </si>
   <si>
+    <t>GILB</t>
+  </si>
+  <si>
+    <t>15,213,326.9</t>
+  </si>
+  <si>
     <t>SIFC</t>
   </si>
   <si>
-    <t>15,009,630.7</t>
-  </si>
-  <si>
-    <t>CHDC</t>
-  </si>
-  <si>
-    <t>14,669,717.0</t>
+    <t>15,016,785.7</t>
   </si>
   <si>
     <t>SHINE</t>
   </si>
   <si>
-    <t>12,921,315.6</t>
+    <t>12,938,189.6</t>
   </si>
   <si>
     <t>SALICOPO</t>
@@ -215,160 +212,154 @@
     <t>17,768,300.0</t>
   </si>
   <si>
+    <t>NRIC</t>
+  </si>
+  <si>
+    <t>13,465,533.1</t>
+  </si>
+  <si>
     <t>SADBL</t>
   </si>
   <si>
-    <t>8,921,953.1</t>
-  </si>
-  <si>
-    <t>ICFC</t>
-  </si>
-  <si>
-    <t>7,940,816.0</t>
+    <t>9,275,953.1</t>
+  </si>
+  <si>
+    <t>UAIL</t>
+  </si>
+  <si>
+    <t>7,864,147.4</t>
+  </si>
+  <si>
+    <t>NFS</t>
+  </si>
+  <si>
+    <t>6,578,298.1</t>
+  </si>
+  <si>
+    <t>JFL</t>
+  </si>
+  <si>
+    <t>87,993,371.1</t>
+  </si>
+  <si>
+    <t>GFCL</t>
+  </si>
+  <si>
+    <t>17,029,261.1</t>
+  </si>
+  <si>
+    <t>5,301,210.7</t>
+  </si>
+  <si>
+    <t>3,854,609.2</t>
+  </si>
+  <si>
+    <t>NMLBBL</t>
+  </si>
+  <si>
+    <t>3,138,809.6</t>
+  </si>
+  <si>
+    <t>GBILD84/85</t>
+  </si>
+  <si>
+    <t>120,169,550.0</t>
+  </si>
+  <si>
+    <t>RLFL</t>
+  </si>
+  <si>
+    <t>5,914,911.7</t>
+  </si>
+  <si>
+    <t>KMCDB</t>
+  </si>
+  <si>
+    <t>5,065,188.0</t>
+  </si>
+  <si>
+    <t>GBLBS</t>
+  </si>
+  <si>
+    <t>3,697,804.0</t>
+  </si>
+  <si>
+    <t>3,348,722.0</t>
+  </si>
+  <si>
+    <t>14,184,721.0</t>
+  </si>
+  <si>
+    <t>HATHY</t>
+  </si>
+  <si>
+    <t>9,330,888.4</t>
+  </si>
+  <si>
+    <t>MKCL</t>
+  </si>
+  <si>
+    <t>7,995,911.4</t>
+  </si>
+  <si>
+    <t>JBBL</t>
+  </si>
+  <si>
+    <t>7,035,244.6</t>
+  </si>
+  <si>
+    <t>5,269,708.0</t>
+  </si>
+  <si>
+    <t>NRM</t>
+  </si>
+  <si>
+    <t>5,179,490.7</t>
   </si>
   <si>
     <t>MLBL</t>
   </si>
   <si>
-    <t>7,084,090.0</t>
-  </si>
-  <si>
-    <t>NRIC</t>
-  </si>
-  <si>
-    <t>7,071,867.4</t>
-  </si>
-  <si>
-    <t>JFL</t>
-  </si>
-  <si>
-    <t>87,993,371.1</t>
-  </si>
-  <si>
-    <t>GFCL</t>
-  </si>
-  <si>
-    <t>17,029,261.1</t>
-  </si>
-  <si>
-    <t>NFS</t>
-  </si>
-  <si>
-    <t>5,301,210.7</t>
-  </si>
-  <si>
-    <t>GILB</t>
-  </si>
-  <si>
-    <t>3,683,287.2</t>
-  </si>
-  <si>
-    <t>NMLBBL</t>
-  </si>
-  <si>
-    <t>3,138,809.6</t>
+    <t>4,835,265.8</t>
+  </si>
+  <si>
+    <t>4,280,149.0</t>
+  </si>
+  <si>
+    <t>ALICL</t>
+  </si>
+  <si>
+    <t>3,849,050.8</t>
   </si>
   <si>
     <t>CKHL</t>
   </si>
   <si>
-    <t>10,318,075.1</t>
-  </si>
-  <si>
-    <t>ALICL</t>
-  </si>
-  <si>
-    <t>8,939,366.8</t>
-  </si>
-  <si>
-    <t>SRLI</t>
-  </si>
-  <si>
-    <t>5,765,573.0</t>
+    <t>3,817,830.8</t>
+  </si>
+  <si>
+    <t>SPIL</t>
+  </si>
+  <si>
+    <t>32,366,822.5</t>
+  </si>
+  <si>
+    <t>HLI</t>
+  </si>
+  <si>
+    <t>8,485,600.0</t>
+  </si>
+  <si>
+    <t>6,650,062.0</t>
   </si>
   <si>
     <t>SHIVM</t>
   </si>
   <si>
-    <t>5,371,163.5</t>
-  </si>
-  <si>
-    <t>NRM</t>
-  </si>
-  <si>
-    <t>5,135,190.7</t>
-  </si>
-  <si>
-    <t>12,237,006.0</t>
-  </si>
-  <si>
-    <t>HATHY</t>
-  </si>
-  <si>
-    <t>9,327,166.19</t>
-  </si>
-  <si>
-    <t>MKCL</t>
-  </si>
-  <si>
-    <t>7,995,911.4</t>
-  </si>
-  <si>
-    <t>JBBL</t>
-  </si>
-  <si>
-    <t>6,028,700.6</t>
-  </si>
-  <si>
-    <t>5,235,080.3</t>
-  </si>
-  <si>
-    <t>SPIL</t>
-  </si>
-  <si>
-    <t>30,683,086.1</t>
-  </si>
-  <si>
-    <t>KRBL</t>
-  </si>
-  <si>
-    <t>29,982,511.2</t>
-  </si>
-  <si>
-    <t>HLI</t>
-  </si>
-  <si>
-    <t>8,485,600.0</t>
-  </si>
-  <si>
-    <t>6,192,632.0</t>
-  </si>
-  <si>
-    <t>5,316,624.9</t>
-  </si>
-  <si>
-    <t>CLI</t>
-  </si>
-  <si>
-    <t>9,553,240.19</t>
-  </si>
-  <si>
-    <t>ALBSL</t>
-  </si>
-  <si>
-    <t>4,752,604.5</t>
-  </si>
-  <si>
-    <t>4,607,793.8</t>
-  </si>
-  <si>
-    <t>GUFL</t>
-  </si>
-  <si>
-    <t>3,505,238.8</t>
-  </si>
-  <si>
-    <t>3,410,141.0</t>
+    <t>5,321,608.9</t>
+  </si>
+  <si>
+    <t>4,694,367.4</t>
   </si>
   <si>
     <t>Sell Amount</t>
@@ -383,7 +374,7 @@
     <t>29,441,700.0</t>
   </si>
   <si>
-    <t>23,172,673.4</t>
+    <t>28,612,469.4</t>
   </si>
   <si>
     <t>MEN</t>
@@ -404,7 +395,7 @@
     <t>10,012,578.0</t>
   </si>
   <si>
-    <t>9,286,035.4</t>
+    <t>9,704,379.4</t>
   </si>
   <si>
     <t>MANDU</t>
@@ -413,10 +404,10 @@
     <t>5,871,046.0</t>
   </si>
   <si>
-    <t>5,049,457.9</t>
-  </si>
-  <si>
-    <t>126,538,445.2</t>
+    <t>4,659,912.5</t>
+  </si>
+  <si>
+    <t>126,663,148.1</t>
   </si>
   <si>
     <t>NICA</t>
@@ -428,16 +419,55 @@
     <t>CITY</t>
   </si>
   <si>
-    <t>3,524,071.0</t>
+    <t>3,349,761.0</t>
   </si>
   <si>
     <t>2,882,798.5</t>
   </si>
   <si>
-    <t>SCB</t>
-  </si>
-  <si>
-    <t>2,775,078.8</t>
+    <t>2,799,307.2</t>
+  </si>
+  <si>
+    <t>119,998,850.0</t>
+  </si>
+  <si>
+    <t>20,417,396.89</t>
+  </si>
+  <si>
+    <t>9,947,244.0</t>
+  </si>
+  <si>
+    <t>EDBL</t>
+  </si>
+  <si>
+    <t>4,233,058.5</t>
+  </si>
+  <si>
+    <t>SGIC</t>
+  </si>
+  <si>
+    <t>3,562,281.3</t>
+  </si>
+  <si>
+    <t>6,566,492.5</t>
+  </si>
+  <si>
+    <t>VLBS</t>
+  </si>
+  <si>
+    <t>6,388,035.9</t>
+  </si>
+  <si>
+    <t>5,754,951.7</t>
+  </si>
+  <si>
+    <t>5,550,570.4</t>
+  </si>
+  <si>
+    <t>SAPDBL</t>
+  </si>
+  <si>
+    <t>4,826,257.8</t>
   </si>
   <si>
     <t>IGI</t>
@@ -446,82 +476,40 @@
     <t>10,810,539.8</t>
   </si>
   <si>
+    <t>9,763,790.0</t>
+  </si>
+  <si>
     <t>7,695,191.3</t>
   </si>
   <si>
-    <t>ILBS</t>
-  </si>
-  <si>
-    <t>7,610,212.0</t>
-  </si>
-  <si>
-    <t>7,120,956.1</t>
-  </si>
-  <si>
-    <t>6,553,776.5</t>
-  </si>
-  <si>
-    <t>VLBS</t>
-  </si>
-  <si>
-    <t>6,357,042.9</t>
-  </si>
-  <si>
-    <t>5,747,691.7</t>
-  </si>
-  <si>
-    <t>5,726,350.4</t>
+    <t>6,593,784.5</t>
+  </si>
+  <si>
+    <t>MLBBL</t>
+  </si>
+  <si>
+    <t>18,782,899.2</t>
+  </si>
+  <si>
+    <t>SWBBL</t>
+  </si>
+  <si>
+    <t>12,808,433.7</t>
+  </si>
+  <si>
+    <t>NMBMF</t>
+  </si>
+  <si>
+    <t>9,789,608.0</t>
+  </si>
+  <si>
+    <t>8,646,035.0</t>
   </si>
   <si>
     <t>GBIME</t>
   </si>
   <si>
-    <t>5,688,882.6</t>
-  </si>
-  <si>
-    <t>MLBBL</t>
-  </si>
-  <si>
-    <t>18,782,899.2</t>
-  </si>
-  <si>
-    <t>SWBBL</t>
-  </si>
-  <si>
-    <t>12,312,119.7</t>
-  </si>
-  <si>
-    <t>NMBMF</t>
-  </si>
-  <si>
-    <t>9,753,948.0</t>
-  </si>
-  <si>
-    <t>8,646,035.0</t>
-  </si>
-  <si>
-    <t>7,278,945.4</t>
-  </si>
-  <si>
-    <t>ACLBSL</t>
-  </si>
-  <si>
-    <t>5,238,120.8</t>
-  </si>
-  <si>
-    <t>5,023,226.4</t>
-  </si>
-  <si>
-    <t>4,262,255.0</t>
-  </si>
-  <si>
-    <t>3,842,225.8</t>
-  </si>
-  <si>
-    <t>SGIC</t>
-  </si>
-  <si>
-    <t>3,376,778.0</t>
+    <t>7,307,613.1</t>
   </si>
   <si>
     <t>Top Traded Stocks</t>
@@ -539,112 +527,112 @@
     <t>Percentage (%)</t>
   </si>
   <si>
-    <t>191,820,298.1</t>
-  </si>
-  <si>
-    <t>163,189,253.9</t>
-  </si>
-  <si>
-    <t>132,864,284.8</t>
+    <t>197,775,931.1</t>
+  </si>
+  <si>
+    <t>162,149,081.3</t>
+  </si>
+  <si>
+    <t>135,644,408.8</t>
   </si>
   <si>
     <t>NGPL</t>
   </si>
   <si>
-    <t>130,460,870.2</t>
-  </si>
-  <si>
-    <t>108,176,841.7</t>
+    <t>131,610,618.2</t>
+  </si>
+  <si>
+    <t>123,643,261.1</t>
   </si>
   <si>
     <t>Promoter Shares/debenture</t>
   </si>
   <si>
-    <t>1,218,921,181.3</t>
+    <t>1,292,650,218.3</t>
   </si>
   <si>
     <t>Microfinance</t>
   </si>
   <si>
-    <t>1,038,874,660.4</t>
+    <t>1,048,348,276.2</t>
+  </si>
+  <si>
+    <t>Hydro Power</t>
+  </si>
+  <si>
+    <t>758,908,631.5</t>
+  </si>
+  <si>
+    <t>Development Banks</t>
+  </si>
+  <si>
+    <t>755,029,773.5</t>
   </si>
   <si>
     <t>Finance</t>
   </si>
   <si>
-    <t>779,771,611.2</t>
-  </si>
-  <si>
-    <t>Hydro Power</t>
-  </si>
-  <si>
-    <t>774,902,958.1</t>
-  </si>
-  <si>
-    <t>Development Banks</t>
-  </si>
-  <si>
-    <t>716,031,054.2</t>
+    <t>734,152,770.6</t>
   </si>
   <si>
     <t>Investment</t>
   </si>
   <si>
-    <t>333,365,270.3</t>
+    <t>350,715,516.3</t>
   </si>
   <si>
     <t>Commercial Banks</t>
   </si>
   <si>
-    <t>231,656,970.9</t>
+    <t>237,969,800.4</t>
   </si>
   <si>
     <t>Non Life Insurance</t>
   </si>
   <si>
-    <t>100,043,825.9</t>
+    <t>93,464,094.4</t>
   </si>
   <si>
     <t>Life Insurance</t>
   </si>
   <si>
-    <t>76,852,170.09</t>
+    <t>72,664,784.7</t>
   </si>
   <si>
     <t>Manufacturing And Processing</t>
   </si>
   <si>
-    <t>56,372,207.9</t>
+    <t>54,880,768.8</t>
   </si>
   <si>
     <t>Hotels And Tourism</t>
   </si>
   <si>
-    <t>48,496,233.3</t>
+    <t>50,343,865.9</t>
   </si>
   <si>
     <t>Others</t>
   </si>
   <si>
-    <t>37,551,901.7</t>
+    <t>44,577,912.0</t>
   </si>
   <si>
     <t>Trading</t>
   </si>
   <si>
-    <t>17,348,875.0</t>
+    <t>35,604,120.0</t>
   </si>
   <si>
     <t>Mutual Fund</t>
   </si>
   <si>
-    <t>4,714,920.21</t>
+    <t>5,178,249.71</t>
   </si>
   <si>
     <t>Tradings</t>
   </si>
   <si>
-    <t>1,389,313.0</t>
+    <t>1,470,103.0</t>
   </si>
   <si>
     <t>Total</t>
@@ -656,214 +644,214 @@
     <t>100%</t>
   </si>
   <si>
-    <t>84,199,322.0</t>
-  </si>
-  <si>
-    <t>61,877,356.7</t>
-  </si>
-  <si>
-    <t>51,690,323.2</t>
-  </si>
-  <si>
-    <t>40,796,591.9</t>
-  </si>
-  <si>
-    <t>36,460,800.4</t>
-  </si>
-  <si>
-    <t>60,944,802.1</t>
-  </si>
-  <si>
-    <t>36,049,880.9</t>
-  </si>
-  <si>
-    <t>25,735,859.9</t>
-  </si>
-  <si>
-    <t>25,442,217.5</t>
-  </si>
-  <si>
-    <t>23,532,504.4</t>
-  </si>
-  <si>
-    <t>113,680,761.1</t>
-  </si>
-  <si>
-    <t>18,054,608.3</t>
-  </si>
-  <si>
-    <t>16,281,948.0</t>
-  </si>
-  <si>
-    <t>13,823,634.4</t>
-  </si>
-  <si>
-    <t>8,827,718.0</t>
-  </si>
-  <si>
-    <t>47,150,016.3</t>
-  </si>
-  <si>
-    <t>27,829,612.9</t>
-  </si>
-  <si>
-    <t>20,973,412.6</t>
-  </si>
-  <si>
-    <t>17,166,145.7</t>
-  </si>
-  <si>
-    <t>13,470,212.5</t>
-  </si>
-  <si>
-    <t>52,127,259.7</t>
-  </si>
-  <si>
-    <t>39,434,551.79</t>
-  </si>
-  <si>
-    <t>25,159,838.9</t>
-  </si>
-  <si>
-    <t>23,925,939.4</t>
-  </si>
-  <si>
-    <t>20,818,149.2</t>
-  </si>
-  <si>
-    <t>58,435,974.1</t>
-  </si>
-  <si>
-    <t>51,635,791.5</t>
-  </si>
-  <si>
-    <t>18,922,025.1</t>
-  </si>
-  <si>
-    <t>9,905,956.5</t>
-  </si>
-  <si>
-    <t>9,025,632.9</t>
-  </si>
-  <si>
-    <t>47,133,434.5</t>
-  </si>
-  <si>
-    <t>30,376,464.5</t>
-  </si>
-  <si>
-    <t>19,730,839.8</t>
-  </si>
-  <si>
-    <t>19,562,297.89</t>
-  </si>
-  <si>
-    <t>18,446,765.8</t>
-  </si>
-  <si>
-    <t>81,937,892.4</t>
-  </si>
-  <si>
-    <t>78,036,629.8</t>
-  </si>
-  <si>
-    <t>72,194,138.09</t>
-  </si>
-  <si>
-    <t>48,953,685.1</t>
-  </si>
-  <si>
-    <t>32,213,447.8</t>
-  </si>
-  <si>
-    <t>54,334,168.6</t>
-  </si>
-  <si>
-    <t>46,818,391.4</t>
-  </si>
-  <si>
-    <t>31,412,601.1</t>
-  </si>
-  <si>
-    <t>20,605,528.89</t>
-  </si>
-  <si>
-    <t>15,809,232.2</t>
-  </si>
-  <si>
-    <t>137,404,097.9</t>
-  </si>
-  <si>
-    <t>15,486,866.8</t>
-  </si>
-  <si>
-    <t>13,800,256.4</t>
-  </si>
-  <si>
-    <t>11,761,619.2</t>
-  </si>
-  <si>
-    <t>11,709,148.9</t>
-  </si>
-  <si>
-    <t>47,381,648.2</t>
-  </si>
-  <si>
-    <t>45,516,373.7</t>
-  </si>
-  <si>
-    <t>37,718,840.2</t>
-  </si>
-  <si>
-    <t>27,899,033.8</t>
-  </si>
-  <si>
-    <t>22,359,857.1</t>
-  </si>
-  <si>
-    <t>39,604,269.9</t>
-  </si>
-  <si>
-    <t>34,670,122.1</t>
-  </si>
-  <si>
-    <t>26,278,920.4</t>
-  </si>
-  <si>
-    <t>25,049,715.5</t>
-  </si>
-  <si>
-    <t>20,448,222.89</t>
-  </si>
-  <si>
-    <t>83,929,635.3</t>
-  </si>
-  <si>
-    <t>20,031,603.39</t>
-  </si>
-  <si>
-    <t>18,754,202.8</t>
-  </si>
-  <si>
-    <t>16,529,000.7</t>
-  </si>
-  <si>
-    <t>14,344,442.2</t>
-  </si>
-  <si>
-    <t>39,930,265.79</t>
-  </si>
-  <si>
-    <t>27,244,440.1</t>
-  </si>
-  <si>
-    <t>21,547,992.8</t>
-  </si>
-  <si>
-    <t>18,785,922.1</t>
-  </si>
-  <si>
-    <t>17,507,131.3</t>
+    <t>83,305,473.59</t>
+  </si>
+  <si>
+    <t>55,421,644.3</t>
+  </si>
+  <si>
+    <t>47,673,852.4</t>
+  </si>
+  <si>
+    <t>46,744,471.7</t>
+  </si>
+  <si>
+    <t>37,273,958.4</t>
+  </si>
+  <si>
+    <t>62,260,378.3</t>
+  </si>
+  <si>
+    <t>36,559,538.2</t>
+  </si>
+  <si>
+    <t>25,515,376.3</t>
+  </si>
+  <si>
+    <t>25,458,843.5</t>
+  </si>
+  <si>
+    <t>15,590,388.0</t>
+  </si>
+  <si>
+    <t>113,280,090.1</t>
+  </si>
+  <si>
+    <t>18,812,286.89</t>
+  </si>
+  <si>
+    <t>16,480,967.7</t>
+  </si>
+  <si>
+    <t>11,324,254.4</t>
+  </si>
+  <si>
+    <t>9,430,895.0</t>
+  </si>
+  <si>
+    <t>132,506,831.4</t>
+  </si>
+  <si>
+    <t>17,908,769.39</t>
+  </si>
+  <si>
+    <t>12,574,429.0</t>
+  </si>
+  <si>
+    <t>10,740,338.2</t>
+  </si>
+  <si>
+    <t>4,608,385.8</t>
+  </si>
+  <si>
+    <t>52,743,214.1</t>
+  </si>
+  <si>
+    <t>42,287,886.0</t>
+  </si>
+  <si>
+    <t>27,556,266.4</t>
+  </si>
+  <si>
+    <t>24,448,474.6</t>
+  </si>
+  <si>
+    <t>20,452,860.2</t>
+  </si>
+  <si>
+    <t>36,938,521.6</t>
+  </si>
+  <si>
+    <t>28,696,569.9</t>
+  </si>
+  <si>
+    <t>24,195,885.8</t>
+  </si>
+  <si>
+    <t>17,312,266.2</t>
+  </si>
+  <si>
+    <t>12,455,185.5</t>
+  </si>
+  <si>
+    <t>60,304,786.5</t>
+  </si>
+  <si>
+    <t>27,260,834.5</t>
+  </si>
+  <si>
+    <t>18,127,275.1</t>
+  </si>
+  <si>
+    <t>13,152,741.9</t>
+  </si>
+  <si>
+    <t>10,790,695.5</t>
+  </si>
+  <si>
+    <t>82,003,819.9</t>
+  </si>
+  <si>
+    <t>80,846,810.89</t>
+  </si>
+  <si>
+    <t>78,351,885.2</t>
+  </si>
+  <si>
+    <t>48,983,781.1</t>
+  </si>
+  <si>
+    <t>34,339,025.79</t>
+  </si>
+  <si>
+    <t>53,194,391.0</t>
+  </si>
+  <si>
+    <t>47,676,196.6</t>
+  </si>
+  <si>
+    <t>31,770,393.3</t>
+  </si>
+  <si>
+    <t>17,490,676.89</t>
+  </si>
+  <si>
+    <t>17,490,580.3</t>
+  </si>
+  <si>
+    <t>137,663,140.8</t>
+  </si>
+  <si>
+    <t>15,855,043.6</t>
+  </si>
+  <si>
+    <t>14,743,534.8</t>
+  </si>
+  <si>
+    <t>13,020,192.4</t>
+  </si>
+  <si>
+    <t>12,684,074.9</t>
+  </si>
+  <si>
+    <t>132,789,385.6</t>
+  </si>
+  <si>
+    <t>20,720,964.3</t>
+  </si>
+  <si>
+    <t>16,662,529.3</t>
+  </si>
+  <si>
+    <t>13,373,149.6</t>
+  </si>
+  <si>
+    <t>11,733,219.4</t>
+  </si>
+  <si>
+    <t>37,128,513.5</t>
+  </si>
+  <si>
+    <t>34,188,561.29</t>
+  </si>
+  <si>
+    <t>27,329,746.8</t>
+  </si>
+  <si>
+    <t>26,663,895.9</t>
+  </si>
+  <si>
+    <t>22,884,107.3</t>
+  </si>
+  <si>
+    <t>54,401,022.1</t>
+  </si>
+  <si>
+    <t>41,523,721.2</t>
+  </si>
+  <si>
+    <t>30,763,403.5</t>
+  </si>
+  <si>
+    <t>28,206,466.3</t>
+  </si>
+  <si>
+    <t>23,898,188.1</t>
+  </si>
+  <si>
+    <t>85,601,817.3</t>
+  </si>
+  <si>
+    <t>18,654,504.3</t>
+  </si>
+  <si>
+    <t>17,840,931.89</t>
+  </si>
+  <si>
+    <t>17,674,530.39</t>
+  </si>
+  <si>
+    <t>17,543,563.2</t>
   </si>
 </sst>
 </file>
@@ -1455,22 +1443,22 @@
       <c r="I4" s="4"/>
       <c r="J4" s="4"/>
       <c r="K4" s="5" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="L4" s="5"/>
       <c r="M4" s="5"/>
       <c r="N4" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O4" s="6"/>
       <c r="P4" s="6"/>
       <c r="Q4" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R4" s="5"/>
       <c r="S4" s="5"/>
       <c r="T4" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="U4" s="6"/>
       <c r="V4" s="6"/>
@@ -1480,37 +1468,37 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
       <c r="E5" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="H5" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
       <c r="K5" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L5" s="5"/>
       <c r="M5" s="5"/>
       <c r="N5" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O5" s="6"/>
       <c r="P5" s="6"/>
       <c r="Q5" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R5" s="5"/>
       <c r="S5" s="5"/>
       <c r="T5" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="U5" s="6"/>
       <c r="V5" s="6"/>
@@ -1520,37 +1508,37 @@
         <v>5</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C6" s="7"/>
       <c r="D6" s="7"/>
       <c r="E6" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F6" s="7"/>
       <c r="G6" s="7"/>
       <c r="H6" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I6" s="7"/>
       <c r="J6" s="7"/>
       <c r="K6" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L6" s="7"/>
       <c r="M6" s="7"/>
       <c r="N6" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O6" s="7"/>
       <c r="P6" s="7"/>
       <c r="Q6" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="R6" s="7"/>
       <c r="S6" s="7"/>
       <c r="T6" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="U6" s="7"/>
       <c r="V6" s="7"/>
@@ -1560,1070 +1548,1070 @@
         <v>6</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
       <c r="E7" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F7" s="8"/>
       <c r="G7" s="8"/>
       <c r="H7" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I7" s="8"/>
       <c r="J7" s="8"/>
       <c r="K7" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L7" s="8"/>
       <c r="M7" s="8"/>
       <c r="N7" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O7" s="8"/>
       <c r="P7" s="8"/>
       <c r="Q7" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="R7" s="8"/>
       <c r="S7" s="8"/>
       <c r="T7" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="U7" s="8"/>
       <c r="V7" s="8"/>
     </row>
     <row r="8" spans="1:22">
       <c r="A8" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>53</v>
-      </c>
       <c r="E8" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="G8" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>53</v>
-      </c>
       <c r="H8" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="I8" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="J8" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="J8" s="4" t="s">
-        <v>53</v>
-      </c>
       <c r="K8" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="L8" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="L8" s="5" t="s">
+      <c r="M8" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="M8" s="5" t="s">
-        <v>53</v>
-      </c>
       <c r="N8" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="O8" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="O8" s="6" t="s">
+      <c r="P8" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="P8" s="6" t="s">
-        <v>53</v>
-      </c>
       <c r="Q8" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="R8" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="R8" s="5" t="s">
+      <c r="S8" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="S8" s="5" t="s">
-        <v>53</v>
-      </c>
       <c r="T8" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="U8" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="U8" s="6" t="s">
+      <c r="V8" s="6" t="s">
         <v>52</v>
-      </c>
-      <c r="V8" s="6" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:22">
       <c r="A9" s="1"/>
       <c r="B9" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C9" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="C9" s="9" t="s">
-        <v>55</v>
-      </c>
       <c r="D9" s="10">
-        <v>0.06252434266264151</v>
+        <v>0.06174571680338291</v>
       </c>
       <c r="E9" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="F9" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="F9" s="11" t="s">
-        <v>65</v>
-      </c>
       <c r="G9" s="12">
-        <v>0.04499352904181024</v>
+        <v>0.04460427440972056</v>
       </c>
       <c r="H9" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="I9" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="I9" s="13" t="s">
-        <v>75</v>
-      </c>
       <c r="J9" s="14">
-        <v>0.225856007077497</v>
+        <v>0.224878031802164</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="M9" s="16">
-        <v>0.02653240378232981</v>
+        <v>0.3096810421861181</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>80</v>
+        <v>57</v>
       </c>
       <c r="O9" s="17" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="P9" s="18">
-        <v>0.03382521592040062</v>
+        <v>0.03806360485853194</v>
       </c>
       <c r="Q9" s="15" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="R9" s="15" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="S9" s="16">
-        <v>0.08757703281505323</v>
+        <v>0.01414492858513821</v>
       </c>
       <c r="T9" s="17" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="U9" s="17" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="V9" s="18">
-        <v>0.03256874326047877</v>
+        <v>0.09674138775075751</v>
       </c>
     </row>
     <row r="10" spans="1:22">
       <c r="A10" s="1"/>
       <c r="B10" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="C10" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="C10" s="9" t="s">
-        <v>57</v>
-      </c>
       <c r="D10" s="10">
-        <v>0.05169923606020875</v>
+        <v>0.05101953522455464</v>
       </c>
       <c r="E10" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="F10" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="F10" s="11" t="s">
-        <v>67</v>
-      </c>
       <c r="G10" s="12">
-        <v>0.02259249089189843</v>
+        <v>0.0338029149364641</v>
       </c>
       <c r="H10" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="I10" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="I10" s="13" t="s">
-        <v>77</v>
-      </c>
       <c r="J10" s="14">
-        <v>0.04370966661971819</v>
+        <v>0.04352040013174532</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="L10" s="15" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="M10" s="16">
-        <v>0.02298712571843498</v>
+        <v>0.01524292984116911</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="O10" s="17" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="P10" s="18">
-        <v>0.02578191190234462</v>
+        <v>0.02503871941060098</v>
       </c>
       <c r="Q10" s="15" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="R10" s="15" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="S10" s="16">
-        <v>0.08557742068976891</v>
+        <v>0.01320486769696511</v>
       </c>
       <c r="T10" s="17" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="U10" s="17" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="V10" s="18">
-        <v>0.01620249805705671</v>
+        <v>0.0253626601714712</v>
       </c>
     </row>
     <row r="11" spans="1:22">
       <c r="A11" s="1"/>
       <c r="B11" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C11" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="C11" s="9" t="s">
-        <v>59</v>
-      </c>
       <c r="D11" s="10">
-        <v>0.02169646945233744</v>
+        <v>0.02170179376171356</v>
       </c>
       <c r="E11" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="F11" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="F11" s="11" t="s">
-        <v>69</v>
-      </c>
       <c r="G11" s="12">
-        <v>0.0201080201995504</v>
+        <v>0.02328569179291761</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="J11" s="14">
-        <v>0.01360682363240545</v>
+        <v>0.01354790495558787</v>
       </c>
       <c r="K11" s="15" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="L11" s="15" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M11" s="16">
-        <v>0.01482587686074301</v>
+        <v>0.01305316279131127</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="O11" s="17" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="P11" s="18">
-        <v>0.02210209176863956</v>
+        <v>0.02145641158634216</v>
       </c>
       <c r="Q11" s="15" t="s">
-        <v>106</v>
+        <v>53</v>
       </c>
       <c r="R11" s="15" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="S11" s="16">
-        <v>0.02421997797853247</v>
+        <v>0.01168887163727328</v>
       </c>
       <c r="T11" s="17" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="U11" s="17" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="V11" s="18">
-        <v>0.01570881189289325</v>
+        <v>0.01987640975596471</v>
       </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1"/>
       <c r="B12" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="C12" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="C12" s="9" t="s">
-        <v>61</v>
-      </c>
       <c r="D12" s="10">
-        <v>0.02120512310572273</v>
+        <v>0.02142142796032664</v>
       </c>
       <c r="E12" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="F12" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="F12" s="11" t="s">
-        <v>71</v>
-      </c>
       <c r="G12" s="12">
-        <v>0.01793858777428328</v>
+        <v>0.01974159534835018</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>80</v>
+        <v>57</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="J12" s="14">
-        <v>0.009454036474705017</v>
+        <v>0.009850934444566516</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="L12" s="15" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="M12" s="16">
-        <v>0.01381167295079213</v>
+        <v>0.009529367435594096</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="O12" s="17" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="P12" s="18">
-        <v>0.01666437848559106</v>
+        <v>0.01887853631647183</v>
       </c>
       <c r="Q12" s="15" t="s">
-        <v>66</v>
+        <v>103</v>
       </c>
       <c r="R12" s="15" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="S12" s="16">
-        <v>0.01767528644635093</v>
+        <v>0.01051156413632891</v>
       </c>
       <c r="T12" s="17" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="U12" s="17" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="V12" s="18">
-        <v>0.01195000022545949</v>
+        <v>0.0159057884057906</v>
       </c>
     </row>
     <row r="13" spans="1:22">
       <c r="A13" s="1"/>
       <c r="B13" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C13" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="C13" s="9" t="s">
-        <v>63</v>
-      </c>
       <c r="D13" s="10">
-        <v>0.01867780325863789</v>
+        <v>0.01845631295473887</v>
       </c>
       <c r="E13" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="F13" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="F13" s="11" t="s">
-        <v>73</v>
-      </c>
       <c r="G13" s="12">
-        <v>0.01790763726646506</v>
+        <v>0.01651369087652411</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="J13" s="14">
-        <v>0.008056504647683803</v>
+        <v>0.008021619313204579</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>92</v>
+        <v>61</v>
       </c>
       <c r="L13" s="15" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="M13" s="16">
-        <v>0.01320488093284617</v>
+        <v>0.008629771177070913</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="O13" s="17" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="P13" s="18">
-        <v>0.01447067375043664</v>
+        <v>0.01414085501095472</v>
       </c>
       <c r="Q13" s="15" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="R13" s="15" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="S13" s="16">
-        <v>0.01517494791153453</v>
+        <v>0.01042630388662366</v>
       </c>
       <c r="T13" s="17" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="U13" s="17" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="V13" s="18">
-        <v>0.01162579443056737</v>
+        <v>0.01403102256602159</v>
       </c>
     </row>
     <row r="15" spans="1:22">
       <c r="A15" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>51</v>
-      </c>
       <c r="C15" s="2" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="M15" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="N15" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q15" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="S15" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="T15" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="U15" s="6" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="V15" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="16" spans="1:22">
       <c r="A16" s="1"/>
       <c r="B16" s="9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D16" s="10">
-        <v>0.1134589886141576</v>
+        <v>0.1119673191959924</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G16" s="12">
-        <v>0.08288763284890337</v>
+        <v>0.0821705431758661</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="J16" s="14">
-        <v>0.3247911475307334</v>
+        <v>0.3237034686876999</v>
       </c>
       <c r="K16" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="L16" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="M16" s="16">
+        <v>0.3092411424452839</v>
+      </c>
+      <c r="N16" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="O16" s="17" t="s">
+        <v>144</v>
+      </c>
+      <c r="P16" s="18">
+        <v>0.01762067620692106</v>
+      </c>
+      <c r="Q16" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="R16" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="L16" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="M16" s="16">
-        <v>0.04569027706781964</v>
-      </c>
-      <c r="N16" s="17" t="s">
-        <v>76</v>
-      </c>
-      <c r="O16" s="17" t="s">
-        <v>147</v>
-      </c>
-      <c r="P16" s="18">
-        <v>0.01811577972639283</v>
-      </c>
-      <c r="Q16" s="15" t="s">
-        <v>154</v>
-      </c>
-      <c r="R16" s="15" t="s">
-        <v>155</v>
-      </c>
       <c r="S16" s="16">
-        <v>0.05361098861565418</v>
+        <v>0.04852433359506009</v>
       </c>
       <c r="T16" s="17" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="U16" s="17" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="V16" s="18">
-        <v>0.01785771193134803</v>
+        <v>0.05614031882773148</v>
       </c>
     </row>
     <row r="17" spans="1:22">
       <c r="A17" s="1"/>
       <c r="B17" s="9" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D17" s="10">
-        <v>0.04255807204336368</v>
+        <v>0.04199855203231334</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="G17" s="12">
-        <v>0.02535421053372525</v>
+        <v>0.02513486246071549</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="J17" s="14">
-        <v>0.01392657974892605</v>
+        <v>0.01386627650155778</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>141</v>
+        <v>53</v>
       </c>
       <c r="L17" s="15" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="M17" s="16">
-        <v>0.02779875163716796</v>
+        <v>0.05261633043245662</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="O17" s="17" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="P17" s="18">
-        <v>0.01757197379062736</v>
+        <v>0.01714180168363667</v>
       </c>
       <c r="Q17" s="15" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="R17" s="15" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="S17" s="16">
-        <v>0.03514180116939943</v>
+        <v>0.02952304044831944</v>
       </c>
       <c r="T17" s="17" t="s">
-        <v>62</v>
+        <v>158</v>
       </c>
       <c r="U17" s="17" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="V17" s="18">
-        <v>0.01712509761461447</v>
+        <v>0.03828320345784853</v>
       </c>
     </row>
     <row r="18" spans="1:22">
       <c r="A18" s="1"/>
       <c r="B18" s="9" t="s">
-        <v>80</v>
+        <v>57</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D18" s="10">
-        <v>0.03349617392998832</v>
+        <v>0.04081565551136222</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="G18" s="12">
-        <v>0.02351443320144178</v>
+        <v>0.0243611826530191</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="J18" s="14">
-        <v>0.009045370063309259</v>
+        <v>0.008560731919584891</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="L18" s="15" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="M18" s="16">
-        <v>0.01978779188706152</v>
+        <v>0.02563438815240309</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="O18" s="17" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="P18" s="18">
-        <v>0.01588762094227906</v>
+        <v>0.01544296905725087</v>
       </c>
       <c r="Q18" s="15" t="s">
-        <v>158</v>
+        <v>105</v>
       </c>
       <c r="R18" s="15" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="S18" s="16">
-        <v>0.02784015340856873</v>
+        <v>0.02666441939364552</v>
       </c>
       <c r="T18" s="17" t="s">
-        <v>74</v>
+        <v>160</v>
       </c>
       <c r="U18" s="17" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="V18" s="18">
-        <v>0.01453080691990681</v>
+        <v>0.0292602174172617</v>
       </c>
     </row>
     <row r="19" spans="1:22">
       <c r="A19" s="1"/>
       <c r="B19" s="9" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D19" s="10">
-        <v>0.02621812999445781</v>
+        <v>0.02587343467157591</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="G19" s="12">
-        <v>0.01486687407950135</v>
+        <v>0.01473825559316829</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="J19" s="14">
-        <v>0.007399391002750182</v>
+        <v>0.007367351024948181</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="L19" s="15" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="M19" s="16">
-        <v>0.01956927195200699</v>
+        <v>0.01090873659687338</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="O19" s="17" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="P19" s="18">
-        <v>0.01582862987203508</v>
+        <v>0.01489452760086459</v>
       </c>
       <c r="Q19" s="15" t="s">
-        <v>56</v>
+        <v>112</v>
       </c>
       <c r="R19" s="15" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="S19" s="16">
-        <v>0.02467789871094807</v>
+        <v>0.02101518038973926</v>
       </c>
       <c r="T19" s="17" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="U19" s="17" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="V19" s="18">
-        <v>0.0130988505480044</v>
+        <v>0.02584218529457505</v>
       </c>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" s="1"/>
       <c r="B20" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D20" s="10">
-        <v>0.01390913816247278</v>
+        <v>0.01372627176921987</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="G20" s="12">
-        <v>0.01278641910982188</v>
+        <v>0.01169791234250249</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>139</v>
+        <v>95</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="J20" s="14">
-        <v>0.007122902660259734</v>
+        <v>0.007153978597208519</v>
       </c>
       <c r="K20" s="15" t="s">
-        <v>86</v>
+        <v>142</v>
       </c>
       <c r="L20" s="15" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="M20" s="16">
-        <v>0.01831117536268412</v>
+        <v>0.00918012080051993</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="O20" s="17" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="P20" s="18">
-        <v>0.0157250623470161</v>
+        <v>0.01295089059873702</v>
       </c>
       <c r="Q20" s="15" t="s">
-        <v>152</v>
+        <v>73</v>
       </c>
       <c r="R20" s="15" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="S20" s="16">
-        <v>0.02077589060230746</v>
+        <v>0.01800729381718772</v>
       </c>
       <c r="T20" s="17" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="U20" s="17" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="V20" s="18">
-        <v>0.01151205386101702</v>
+        <v>0.02184176813895201</v>
       </c>
     </row>
     <row r="23" spans="1:22">
       <c r="B23" s="19" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
     </row>
     <row r="24" spans="1:22">
       <c r="B24" s="20" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
     </row>
     <row r="25" spans="1:22">
       <c r="B25" s="20" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="26" spans="1:22">
       <c r="B26" s="20" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C26" s="21" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
     </row>
     <row r="27" spans="1:22">
       <c r="B27" s="20" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
     </row>
     <row r="28" spans="1:22">
       <c r="B28" s="20" t="s">
-        <v>80</v>
+        <v>57</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
     </row>
     <row r="30" spans="1:22">
       <c r="B30" s="19" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="D30" s="19" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
     </row>
     <row r="31" spans="1:22">
       <c r="B31" s="20" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C31" s="21" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="D31" s="22">
-        <v>0.2201824844715665</v>
+        <v>0.2335006897775424</v>
       </c>
     </row>
     <row r="32" spans="1:22">
       <c r="B32" s="20" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="C32" s="21" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="D32" s="22">
-        <v>0.1876593887206634</v>
+        <v>0.1893706759603752</v>
       </c>
     </row>
     <row r="33" spans="2:4">
       <c r="B33" s="20" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C33" s="21" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="D33" s="22">
-        <v>0.1408557446604546</v>
+        <v>0.1370871148472236</v>
       </c>
     </row>
     <row r="34" spans="2:4">
       <c r="B34" s="20" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="C34" s="21" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="D34" s="22">
-        <v>0.1399762848955131</v>
+        <v>0.1363864488776311</v>
       </c>
     </row>
     <row r="35" spans="2:4">
       <c r="B35" s="20" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C35" s="21" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="D35" s="22">
-        <v>0.129341830211209</v>
+        <v>0.1326152859531017</v>
       </c>
     </row>
     <row r="36" spans="2:4">
       <c r="B36" s="20" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="C36" s="21" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="D36" s="22">
-        <v>0.06021816223827182</v>
+        <v>0.06335226174288337</v>
       </c>
     </row>
     <row r="37" spans="2:4">
       <c r="B37" s="20" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C37" s="21" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="D37" s="22">
-        <v>0.04184586188216023</v>
+        <v>0.04298619359899279</v>
       </c>
     </row>
     <row r="38" spans="2:4">
       <c r="B38" s="20" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C38" s="21" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="D38" s="22">
-        <v>0.01807163455737945</v>
+        <v>0.01688309041600952</v>
       </c>
     </row>
     <row r="39" spans="2:4">
       <c r="B39" s="20" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="C39" s="21" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="D39" s="22">
-        <v>0.01388235926100027</v>
+        <v>0.01312596177201033</v>
       </c>
     </row>
     <row r="40" spans="2:4">
       <c r="B40" s="20" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="C40" s="21" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="D40" s="22">
-        <v>0.01018291664874662</v>
+        <v>0.009913507296022269</v>
       </c>
     </row>
     <row r="41" spans="2:4">
       <c r="B41" s="20" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="C41" s="21" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="D41" s="22">
-        <v>0.008760222809581853</v>
+        <v>0.009093973951575123</v>
       </c>
     </row>
     <row r="42" spans="2:4">
       <c r="B42" s="20" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="C42" s="21" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="D42" s="22">
-        <v>0.006783269615611892</v>
+        <v>0.00805242830077553</v>
       </c>
     </row>
     <row r="43" spans="2:4">
       <c r="B43" s="20" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="C43" s="21" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="D43" s="22">
-        <v>0.003133851851038179</v>
+        <v>0.006431427822644722</v>
       </c>
     </row>
     <row r="44" spans="2:4">
       <c r="B44" s="20" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="C44" s="21" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D44" s="22">
-        <v>0.0008516898892640486</v>
+        <v>0.0009353844234177383</v>
       </c>
     </row>
     <row r="45" spans="2:4">
       <c r="B45" s="20" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="C45" s="21" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="D45" s="22">
-        <v>0.0002509615820461791</v>
+        <v>0.0002655552597944697</v>
       </c>
     </row>
     <row r="46" spans="2:4">
       <c r="B46" s="20" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C46" s="20" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="D46" s="20" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
   </sheetData>
@@ -2791,22 +2779,22 @@
       <c r="I4" s="4"/>
       <c r="J4" s="4"/>
       <c r="K4" s="5" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="L4" s="5"/>
       <c r="M4" s="5"/>
       <c r="N4" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O4" s="6"/>
       <c r="P4" s="6"/>
       <c r="Q4" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R4" s="5"/>
       <c r="S4" s="5"/>
       <c r="T4" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="U4" s="6"/>
       <c r="V4" s="6"/>
@@ -2816,37 +2804,37 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
       <c r="E5" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="H5" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
       <c r="K5" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L5" s="5"/>
       <c r="M5" s="5"/>
       <c r="N5" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O5" s="6"/>
       <c r="P5" s="6"/>
       <c r="Q5" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R5" s="5"/>
       <c r="S5" s="5"/>
       <c r="T5" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="U5" s="6"/>
       <c r="V5" s="6"/>
@@ -2856,37 +2844,37 @@
         <v>5</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C6" s="7"/>
       <c r="D6" s="7"/>
       <c r="E6" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F6" s="7"/>
       <c r="G6" s="7"/>
       <c r="H6" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I6" s="7"/>
       <c r="J6" s="7"/>
       <c r="K6" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L6" s="7"/>
       <c r="M6" s="7"/>
       <c r="N6" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O6" s="7"/>
       <c r="P6" s="7"/>
       <c r="Q6" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="R6" s="7"/>
       <c r="S6" s="7"/>
       <c r="T6" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="U6" s="7"/>
       <c r="V6" s="7"/>
@@ -2896,371 +2884,371 @@
         <v>6</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
       <c r="E7" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F7" s="8"/>
       <c r="G7" s="8"/>
       <c r="H7" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I7" s="8"/>
       <c r="J7" s="8"/>
       <c r="K7" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L7" s="8"/>
       <c r="M7" s="8"/>
       <c r="N7" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O7" s="8"/>
       <c r="P7" s="8"/>
       <c r="Q7" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="R7" s="8"/>
       <c r="S7" s="8"/>
       <c r="T7" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="U7" s="8"/>
       <c r="V7" s="8"/>
     </row>
     <row r="8" spans="1:22">
       <c r="A8" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>53</v>
-      </c>
       <c r="E8" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="G8" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>53</v>
-      </c>
       <c r="H8" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="I8" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="J8" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="J8" s="4" t="s">
-        <v>53</v>
-      </c>
       <c r="K8" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="L8" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="L8" s="5" t="s">
+      <c r="M8" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="M8" s="5" t="s">
-        <v>53</v>
-      </c>
       <c r="N8" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="O8" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="O8" s="6" t="s">
+      <c r="P8" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="P8" s="6" t="s">
-        <v>53</v>
-      </c>
       <c r="Q8" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="R8" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="R8" s="5" t="s">
+      <c r="S8" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="S8" s="5" t="s">
-        <v>53</v>
-      </c>
       <c r="T8" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="U8" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="U8" s="6" t="s">
+      <c r="V8" s="6" t="s">
         <v>52</v>
-      </c>
-      <c r="V8" s="6" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:22">
       <c r="A9" s="1"/>
       <c r="B9" s="9" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="D9" s="10">
-        <v>0.1217103907613479</v>
+        <v>0.1188351646666499</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="G9" s="12">
-        <v>0.1543266223124175</v>
+        <v>0.1562940179165261</v>
       </c>
       <c r="H9" s="13" t="s">
         <v>184</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="J9" s="14">
-        <v>0.2917888298017128</v>
+        <v>0.289501395225666</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="M9" s="16">
-        <v>0.1212438617368691</v>
+        <v>0.3414746384981241</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="O9" s="17" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="P9" s="18">
-        <v>0.1440888248883181</v>
+        <v>0.1415323474089727</v>
       </c>
       <c r="Q9" s="15" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="R9" s="15" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="S9" s="16">
-        <v>0.1667905635259845</v>
+        <v>0.1008772445662631</v>
       </c>
       <c r="T9" s="17" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="U9" s="17" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="V9" s="18">
-        <v>0.1606864995622211</v>
+        <v>0.1802453340615424</v>
       </c>
     </row>
     <row r="10" spans="1:22">
       <c r="A10" s="1"/>
       <c r="B10" s="9" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="D10" s="10">
-        <v>0.08944391812604274</v>
+        <v>0.07905891344079696</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="G10" s="12">
-        <v>0.09128680646026632</v>
+        <v>0.09177645999704311</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="J10" s="14">
-        <v>0.04634146514686988</v>
+        <v>0.04807714489040223</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="L10" s="15" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="M10" s="16">
-        <v>0.07156242995059559</v>
+        <v>0.04615151152736164</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="O10" s="17" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="P10" s="18">
-        <v>0.109003969546082</v>
+        <v>0.1134762807817401</v>
       </c>
       <c r="Q10" s="15" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="R10" s="15" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="S10" s="16">
-        <v>0.1473811790603015</v>
+        <v>0.07836888902492417</v>
       </c>
       <c r="T10" s="17" t="s">
         <v>182</v>
       </c>
       <c r="U10" s="17" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="V10" s="18">
-        <v>0.103558923752545</v>
+        <v>0.0814800699319103</v>
       </c>
     </row>
     <row r="11" spans="1:22">
       <c r="A11" s="1"/>
       <c r="B11" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="D11" s="10">
+        <v>0.06800669698428508</v>
+      </c>
+      <c r="E11" s="11" t="s">
         <v>180</v>
       </c>
-      <c r="C11" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="D11" s="10">
-        <v>0.07471852843722859</v>
-      </c>
-      <c r="E11" s="11" t="s">
-        <v>186</v>
-      </c>
       <c r="F11" s="11" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="G11" s="12">
-        <v>0.06516927110790618</v>
+        <v>0.06405198280941228</v>
       </c>
       <c r="H11" s="13" t="s">
+        <v>178</v>
+      </c>
+      <c r="I11" s="13" t="s">
+        <v>221</v>
+      </c>
+      <c r="J11" s="14">
+        <v>0.04211916798095075</v>
+      </c>
+      <c r="K11" s="15" t="s">
         <v>182</v>
       </c>
-      <c r="I11" s="13" t="s">
-        <v>225</v>
-      </c>
-      <c r="J11" s="14">
-        <v>0.04179150902792766</v>
-      </c>
-      <c r="K11" s="15" t="s">
-        <v>188</v>
-      </c>
       <c r="L11" s="15" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="M11" s="16">
-        <v>0.05393206062210226</v>
+        <v>0.03240473379167474</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="O11" s="17" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="P11" s="18">
-        <v>0.06954617684382886</v>
+        <v>0.07394511570767168</v>
       </c>
       <c r="Q11" s="15" t="s">
         <v>182</v>
       </c>
       <c r="R11" s="15" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="S11" s="16">
-        <v>0.05400808796446199</v>
+        <v>0.06607774712196313</v>
       </c>
       <c r="T11" s="17" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="U11" s="17" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="V11" s="18">
-        <v>0.06726604191945643</v>
+        <v>0.05418072006647399</v>
       </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1"/>
       <c r="B12" s="9" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="D12" s="10">
-        <v>0.05897160480556174</v>
+        <v>0.0666809364579983</v>
       </c>
       <c r="E12" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>217</v>
+      </c>
+      <c r="G12" s="12">
+        <v>0.06391006689599626</v>
+      </c>
+      <c r="H12" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="I12" s="13" t="s">
+        <v>222</v>
+      </c>
+      <c r="J12" s="14">
+        <v>0.02894054414854661</v>
+      </c>
+      <c r="K12" s="15" t="s">
         <v>184</v>
       </c>
-      <c r="F12" s="11" t="s">
-        <v>221</v>
-      </c>
-      <c r="G12" s="12">
-        <v>0.06442569924946689</v>
-      </c>
-      <c r="H12" s="13" t="s">
-        <v>186</v>
-      </c>
-      <c r="I12" s="13" t="s">
-        <v>226</v>
-      </c>
-      <c r="J12" s="14">
-        <v>0.03548165992339316</v>
-      </c>
-      <c r="K12" s="15" t="s">
-        <v>186</v>
-      </c>
       <c r="L12" s="15" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="M12" s="16">
-        <v>0.04414186800197884</v>
+        <v>0.02767821904307186</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="O12" s="17" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="P12" s="18">
-        <v>0.06613546371583216</v>
+        <v>0.06560559608950044</v>
       </c>
       <c r="Q12" s="15" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="R12" s="15" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="S12" s="16">
-        <v>0.02827402284886166</v>
+        <v>0.04727892822471949</v>
       </c>
       <c r="T12" s="17" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="U12" s="17" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="V12" s="18">
-        <v>0.06669145175373095</v>
+        <v>0.03931230827905752</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -3269,396 +3257,396 @@
         <v>184</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="D13" s="10">
-        <v>0.05270420424710201</v>
+        <v>0.05317125985634942</v>
       </c>
       <c r="E13" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="G13" s="12">
+        <v>0.03913699929121044</v>
+      </c>
+      <c r="H13" s="13" t="s">
         <v>182</v>
       </c>
-      <c r="F13" s="11" t="s">
-        <v>222</v>
-      </c>
-      <c r="G13" s="12">
-        <v>0.05958985497475432</v>
-      </c>
-      <c r="H13" s="13" t="s">
-        <v>188</v>
-      </c>
       <c r="I13" s="13" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="J13" s="14">
-        <v>0.02265844704165617</v>
+        <v>0.02410182811751452</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="L13" s="15" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="M13" s="16">
-        <v>0.03463796431214058</v>
+        <v>0.01187596789153082</v>
       </c>
       <c r="N13" s="17" t="s">
         <v>184</v>
       </c>
       <c r="O13" s="17" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="P13" s="18">
-        <v>0.05754499031487894</v>
+        <v>0.05488367299431512</v>
       </c>
       <c r="Q13" s="15" t="s">
+        <v>184</v>
+      </c>
+      <c r="R13" s="15" t="s">
+        <v>238</v>
+      </c>
+      <c r="S13" s="16">
+        <v>0.03401448513309407</v>
+      </c>
+      <c r="T13" s="17" t="s">
         <v>186</v>
       </c>
-      <c r="R13" s="15" t="s">
-        <v>242</v>
-      </c>
-      <c r="S13" s="16">
-        <v>0.02576136396722897</v>
-      </c>
-      <c r="T13" s="17" t="s">
-        <v>188</v>
-      </c>
       <c r="U13" s="17" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="V13" s="18">
-        <v>0.0628883987787076</v>
+        <v>0.03225237378386013</v>
       </c>
     </row>
     <row r="15" spans="1:22">
       <c r="A15" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>51</v>
-      </c>
       <c r="C15" s="2" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="M15" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="N15" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q15" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="S15" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="T15" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="U15" s="6" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="V15" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="16" spans="1:22">
       <c r="A16" s="1"/>
       <c r="B16" s="9" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D16" s="10">
-        <v>0.11844148700111</v>
+        <v>0.1169783571233523</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="G16" s="12">
-        <v>0.137586938135146</v>
+        <v>0.1335354093088235</v>
       </c>
       <c r="H16" s="13" t="s">
         <v>184</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="J16" s="14">
-        <v>0.3526804408085634</v>
+        <v>0.3518153216294742</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="L16" s="15" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="M16" s="16">
-        <v>0.1218394913518996</v>
+        <v>0.3422027903396685</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="O16" s="17" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="P16" s="18">
-        <v>0.1094730999345202</v>
+        <v>0.09963150257581159</v>
       </c>
       <c r="Q16" s="15" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="R16" s="15" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="S16" s="16">
-        <v>0.2395557083426347</v>
+        <v>0.1485664551078402</v>
       </c>
       <c r="T16" s="17" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="U16" s="17" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="V16" s="18">
-        <v>0.1361295799055566</v>
+        <v>0.2558557794664213</v>
       </c>
     </row>
     <row r="17" spans="1:22">
       <c r="A17" s="1"/>
       <c r="B17" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="D17" s="10">
+        <v>0.1153278850823915</v>
+      </c>
+      <c r="E17" s="11" t="s">
         <v>180</v>
       </c>
-      <c r="C17" s="9" t="s">
-        <v>249</v>
-      </c>
-      <c r="D17" s="10">
-        <v>0.112802199365176</v>
-      </c>
-      <c r="E17" s="11" t="s">
+      <c r="F17" s="11" t="s">
+        <v>250</v>
+      </c>
+      <c r="G17" s="12">
+        <v>0.1196829272332292</v>
+      </c>
+      <c r="H17" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="I17" s="13" t="s">
+        <v>255</v>
+      </c>
+      <c r="J17" s="14">
+        <v>0.04051954089647892</v>
+      </c>
+      <c r="K17" s="15" t="s">
         <v>186</v>
       </c>
-      <c r="F17" s="11" t="s">
-        <v>254</v>
-      </c>
-      <c r="G17" s="12">
-        <v>0.1185552164892949</v>
-      </c>
-      <c r="H17" s="13" t="s">
-        <v>180</v>
-      </c>
-      <c r="I17" s="13" t="s">
-        <v>259</v>
-      </c>
-      <c r="J17" s="14">
-        <v>0.03975074319648442</v>
-      </c>
-      <c r="K17" s="15" t="s">
-        <v>180</v>
-      </c>
       <c r="L17" s="15" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="M17" s="16">
-        <v>0.1170430331250271</v>
+        <v>0.05339863400940877</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="O17" s="17" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="P17" s="18">
-        <v>0.09583425602791676</v>
+        <v>0.09174236758022219</v>
       </c>
       <c r="Q17" s="15" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="R17" s="15" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="S17" s="16">
-        <v>0.05717509583561517</v>
+        <v>0.1133991940487874</v>
       </c>
       <c r="T17" s="17" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="U17" s="17" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="V17" s="18">
-        <v>0.09288127968271882</v>
+        <v>0.05575655854956023</v>
       </c>
     </row>
     <row r="18" spans="1:22">
       <c r="A18" s="1"/>
       <c r="B18" s="9" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="D18" s="10">
-        <v>0.1043568588216151</v>
+        <v>0.1117688763693007</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="G18" s="12">
-        <v>0.07954411957652957</v>
+        <v>0.07975413184479929</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="J18" s="14">
-        <v>0.03542165470177872</v>
+        <v>0.037678941563255</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="L18" s="15" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="M18" s="16">
-        <v>0.09699207349126329</v>
+        <v>0.04293990814711988</v>
       </c>
       <c r="N18" s="17" t="s">
         <v>184</v>
       </c>
       <c r="O18" s="17" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="P18" s="18">
-        <v>0.07263951302181437</v>
+        <v>0.07333726783057119</v>
       </c>
       <c r="Q18" s="15" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="R18" s="15" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="S18" s="16">
-        <v>0.05352908207091213</v>
+        <v>0.08401330762951094</v>
       </c>
       <c r="T18" s="17" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="U18" s="17" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="V18" s="18">
-        <v>0.07346104887866685</v>
+        <v>0.05332486717757848</v>
       </c>
     </row>
     <row r="19" spans="1:22">
       <c r="A19" s="1"/>
       <c r="B19" s="9" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="D19" s="10">
-        <v>0.07076270926182725</v>
+        <v>0.06987530880580255</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="G19" s="12">
-        <v>0.05217806222227282</v>
+        <v>0.04390734915885933</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="J19" s="14">
-        <v>0.0301890053315394</v>
+        <v>0.03327472517526373</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="L19" s="15" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="M19" s="16">
-        <v>0.07174094225370266</v>
+        <v>0.03446306410766179</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="O19" s="17" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="P19" s="18">
-        <v>0.06924177658588271</v>
+        <v>0.07155050829174785</v>
       </c>
       <c r="Q19" s="15" t="s">
         <v>184</v>
       </c>
       <c r="R19" s="15" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="S19" s="16">
-        <v>0.0471778109928759</v>
+        <v>0.07703044074441676</v>
       </c>
       <c r="T19" s="17" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="U19" s="17" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="V19" s="18">
-        <v>0.06404464464174724</v>
+        <v>0.05282750874723496</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -3667,64 +3655,64 @@
         <v>184</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="D20" s="10">
-        <v>0.04656464240303839</v>
+        <v>0.04898458179385871</v>
       </c>
       <c r="E20" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="F20" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="G20" s="12">
+        <v>0.04390710666110165</v>
+      </c>
+      <c r="H20" s="13" t="s">
+        <v>188</v>
+      </c>
+      <c r="I20" s="13" t="s">
+        <v>258</v>
+      </c>
+      <c r="J20" s="14">
+        <v>0.03241573499328326</v>
+      </c>
+      <c r="K20" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="L20" s="15" t="s">
+        <v>263</v>
+      </c>
+      <c r="M20" s="16">
+        <v>0.03023690786884348</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>180</v>
+      </c>
+      <c r="O20" s="17" t="s">
+        <v>268</v>
+      </c>
+      <c r="P20" s="18">
+        <v>0.06140773708608342</v>
+      </c>
+      <c r="Q20" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="R20" s="15" t="s">
+        <v>273</v>
+      </c>
+      <c r="S20" s="16">
+        <v>0.06526474967677805</v>
+      </c>
+      <c r="T20" s="17" t="s">
         <v>184</v>
       </c>
-      <c r="F20" s="11" t="s">
-        <v>257</v>
-      </c>
-      <c r="G20" s="12">
-        <v>0.04003270701864678</v>
-      </c>
-      <c r="H20" s="13" t="s">
-        <v>192</v>
-      </c>
-      <c r="I20" s="13" t="s">
-        <v>262</v>
-      </c>
-      <c r="J20" s="14">
-        <v>0.03005432777230951</v>
-      </c>
-      <c r="K20" s="15" t="s">
-        <v>186</v>
-      </c>
-      <c r="L20" s="15" t="s">
-        <v>267</v>
-      </c>
-      <c r="M20" s="16">
-        <v>0.0574972319296643</v>
-      </c>
-      <c r="N20" s="17" t="s">
-        <v>186</v>
-      </c>
-      <c r="O20" s="17" t="s">
-        <v>272</v>
-      </c>
-      <c r="P20" s="18">
-        <v>0.05652244959109937</v>
-      </c>
-      <c r="Q20" s="15" t="s">
-        <v>188</v>
-      </c>
-      <c r="R20" s="15" t="s">
-        <v>277</v>
-      </c>
-      <c r="S20" s="16">
-        <v>0.04094254669066793</v>
-      </c>
-      <c r="T20" s="17" t="s">
-        <v>188</v>
-      </c>
       <c r="U20" s="17" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="V20" s="18">
-        <v>0.05968501289616815</v>
+        <v>0.05243606010633636</v>
       </c>
     </row>
   </sheetData>
